--- a/data/output/df_ML_best_models.xlsx
+++ b/data/output/df_ML_best_models.xlsx
@@ -468,54 +468,54 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'learning_rate': 0.095, 'n_estimators': 1900, 'subsample': 0.6799999999999999, 'colsample_bytree': 0.8400000000000001, 'gamma': 23.5, 'reg_alpha': 14.5, 'reg_lambda': 23.5, 'min_child_weight': 8}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.14</v>
+        <v>21.69</v>
       </c>
       <c r="D2" t="n">
-        <v>11.97</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SKU4</t>
+          <t>SKU16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_depth': 9, 'min_samples_split': 4, 'min_samples_leaf': 5, 'max_features': 'sqrt', 'bootstrap': True}</t>
+          <t>{'max_depth': 5, 'learning_rate': 0.057, 'n_estimators': 50, 'subsample': 0.6799999999999999, 'colsample_bytree': 0.72, 'gamma': 22.0, 'reg_alpha': 21.0, 'reg_lambda': 17.5, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.1</v>
+        <v>22.45</v>
       </c>
       <c r="D3" t="n">
-        <v>8.859999999999999</v>
+        <v>13.83</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SKU3</t>
+          <t>SKU4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.62</v>
+        <v>22.9</v>
       </c>
       <c r="D4" t="n">
-        <v>10.68</v>
+        <v>4.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -541,97 +541,97 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SKU16</t>
+          <t>SKU2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.10558813779064824, 'model__l1_ratio': 0.29}</t>
+          <t>{'max_depth': 4, 'learning_rate': 0.075, 'n_estimators': 150, 'subsample': 0.66, 'colsample_bytree': 0.8, 'gamma': 7.0, 'reg_alpha': 21.5, 'reg_lambda': 13.0, 'min_child_weight': 19}</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.88</v>
+        <v>24.01</v>
       </c>
       <c r="D5" t="n">
-        <v>14.66</v>
+        <v>7.27</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SKU2</t>
+          <t>SKU6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'learning_rate': 0.02, 'n_estimators': 1350, 'subsample': 0.54, 'colsample_bytree': 0.8, 'gamma': 1.0, 'reg_alpha': 14.5, 'reg_lambda': 16.0, 'min_child_weight': 19}</t>
+          <t>{'model__alpha': 0.000139345022513376, 'model__l1_ratio': 0.97}</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24.81</v>
+        <v>25.8</v>
       </c>
       <c r="D6" t="n">
-        <v>12.56</v>
+        <v>5.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SKU23</t>
+          <t>SKU1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 250, 'max_depth': 7, 'min_samples_split': 3, 'min_samples_leaf': 15, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.057, 'n_estimators': 950, 'subsample': 0.5, 'colsample_bytree': 1.0, 'gamma': 21.0, 'reg_alpha': 29.5, 'reg_lambda': 19.0, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24.83</v>
+        <v>26.01</v>
       </c>
       <c r="D7" t="n">
-        <v>11.49</v>
+        <v>21.73</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SKU6</t>
+          <t>SKU3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.00011293569666047012, 'model__l1_ratio': 0.98}</t>
+          <t>{'model__alpha': 1.6136341713591302, 'model__l1_ratio': 0.71}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25.8</v>
+        <v>27.24</v>
       </c>
       <c r="D8" t="n">
-        <v>4.81</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -645,45 +645,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SKU10</t>
+          <t>SKU24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'learning_rate': 0.076, 'n_estimators': 100, 'subsample': 0.58, 'colsample_bytree': 0.66, 'gamma': 1.0, 'reg_alpha': 21.0, 'reg_lambda': 24.5, 'min_child_weight': 16}</t>
+          <t>{'n_estimators': 500, 'max_depth': 6, 'min_samples_split': 9, 'min_samples_leaf': 15, 'max_features': None, 'bootstrap': False}</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25.84</v>
+        <v>27.31</v>
       </c>
       <c r="D9" t="n">
-        <v>3.78</v>
+        <v>5.41</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SKU17</t>
+          <t>SKU11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0012363188277052211, 'model__l1_ratio': 0.15}</t>
+          <t>{'model__alpha': 8.117770337590418, 'model__l1_ratio': 1.0}</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.54</v>
+        <v>27.92</v>
       </c>
       <c r="D10" t="n">
-        <v>21.25</v>
+        <v>4.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.46</v>
+        <v>29.96</v>
       </c>
       <c r="D11" t="n">
-        <v>16.67</v>
+        <v>14.47</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -723,59 +723,59 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SKU1</t>
+          <t>SKU10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'max_depth': 2, 'learning_rate': 0.021, 'n_estimators': 2800, 'subsample': 0.9, 'colsample_bytree': 0.98, 'gamma': 2.0, 'reg_alpha': 5.0, 'reg_lambda': 6.5, 'min_child_weight': 6}</t>
+          <t>{'model__alpha': 0.0005551555004438736, 'model__l1_ratio': 0.27}</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>27.46</v>
+        <v>29.99</v>
       </c>
       <c r="D12" t="n">
-        <v>1.83</v>
+        <v>3.11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SKU21</t>
+          <t>SKU25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.017, 'n_estimators': 2650, 'subsample': 0.98, 'colsample_bytree': 0.74, 'gamma': 13.5, 'reg_alpha': 9.0, 'reg_lambda': 3.5, 'min_child_weight': 6}</t>
+          <t>{'model__alpha': 1.568513385619359, 'model__l1_ratio': 0.65}</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.62</v>
+        <v>31.31</v>
       </c>
       <c r="D13" t="n">
-        <v>4.12</v>
+        <v>7.57</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SKU11</t>
+          <t>SKU17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>29.89</v>
+        <v>31.77</v>
       </c>
       <c r="D14" t="n">
-        <v>3.42</v>
+        <v>16.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -801,175 +801,175 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SKU22</t>
+          <t>SKU23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 5, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 29, 'model__algorithm': 'auto'}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31.92</v>
+        <v>33.15</v>
       </c>
       <c r="D15" t="n">
-        <v>18.31</v>
+        <v>5.21</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KNeighborsRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SKU14</t>
+          <t>SKU22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'max_depth': 1, 'learning_rate': 0.063, 'n_estimators': 3000, 'subsample': 0.62, 'colsample_bytree': 0.74, 'gamma': 26.0, 'reg_alpha': 7.0, 'reg_lambda': 10.5, 'min_child_weight': 14}</t>
+          <t>{'model__alpha': 0.4477261164915934, 'model__l1_ratio': 0.36}</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34.84</v>
+        <v>33.58</v>
       </c>
       <c r="D16" t="n">
-        <v>14.82</v>
+        <v>15.08</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SKU24</t>
+          <t>SKU21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'model__alpha': 309.9764189324157, 'model__l1_ratio': 1.0}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.098, 'n_estimators': 100, 'subsample': 0.96, 'colsample_bytree': 0.86, 'gamma': 24.0, 'reg_alpha': 12.5, 'reg_lambda': 17.5, 'min_child_weight': 5}</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35.43</v>
+        <v>34.12</v>
       </c>
       <c r="D17" t="n">
-        <v>9.640000000000001</v>
+        <v>4.79</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SKU13</t>
+          <t>SKU14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 1000, 'max_depth': 7, 'min_samples_split': 5, 'min_samples_leaf': 3, 'max_features': None, 'bootstrap': False}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.077, 'n_estimators': 2300, 'subsample': 0.72, 'colsample_bytree': 0.8, 'gamma': 3.5, 'reg_alpha': 26.0, 'reg_lambda': 14.5, 'min_child_weight': 17}</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37.38</v>
+        <v>41.62</v>
       </c>
       <c r="D18" t="n">
-        <v>10.28</v>
+        <v>20.02</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SKU25</t>
+          <t>SKU13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'model__alpha': 1.6136341713591302, 'model__l1_ratio': 0.71}</t>
+          <t>{'n_estimators': 400, 'max_depth': 10, 'min_samples_split': 8, 'min_samples_leaf': 10, 'max_features': 'sqrt', 'bootstrap': True}</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.47</v>
+        <v>42.19</v>
       </c>
       <c r="D19" t="n">
-        <v>2.37</v>
+        <v>20.24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>RandomForestRegressor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SKU12</t>
+          <t>SKU7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.009349170414488468, 'model__l1_ratio': 0.08}</t>
+          <t>{'max_depth': 1, 'learning_rate': 0.069, 'n_estimators': 600, 'subsample': 0.94, 'colsample_bytree': 0.8200000000000001, 'gamma': 20.0, 'reg_alpha': 4.0, 'reg_lambda': 19.0, 'min_child_weight': 15}</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38.76</v>
+        <v>44.58</v>
       </c>
       <c r="D20" t="n">
-        <v>17.16</v>
+        <v>16.23</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SKU18</t>
+          <t>SKU8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 25, 'model__algorithm': 'auto'}</t>
+          <t>{'model__n_neighbors': 3, 'model__weights': 'uniform', 'model__p': 2, 'model__leaf_size': 18, 'model__algorithm': 'kd_tree'}</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>41.05</v>
+        <v>49.97</v>
       </c>
       <c r="D21" t="n">
-        <v>12.04</v>
+        <v>16.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -977,77 +977,77 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SKU15</t>
+          <t>SKU9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'max_depth': 3, 'learning_rate': 0.028, 'n_estimators': 2700, 'subsample': 0.52, 'colsample_bytree': 0.7, 'gamma': 10.0, 'reg_alpha': 5.0, 'reg_lambda': 27.5, 'min_child_weight': 19}</t>
+          <t>{'model__alpha': 0.06032030579768781, 'model__l1_ratio': 0.03}</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>43.36</v>
+        <v>50.18</v>
       </c>
       <c r="D22" t="n">
-        <v>20.57</v>
+        <v>8.58</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>XGBRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SKU7</t>
+          <t>SKU20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 550, 'max_depth': 6, 'min_samples_split': 2, 'min_samples_leaf': 10, 'max_features': None, 'bootstrap': True}</t>
+          <t>{'model__alpha': 0.00011482217479097196, 'model__l1_ratio': 1.0}</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46.23</v>
+        <v>53.09</v>
       </c>
       <c r="D23" t="n">
-        <v>14.7</v>
+        <v>16.05</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RandomForestRegressor</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SKU9</t>
+          <t>SKU12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.06032030579768781, 'model__l1_ratio': 0.03}</t>
+          <t>{'model__alpha': 0.041858227295469716, 'model__l1_ratio': 0.96}</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50.18</v>
+        <v>53.7</v>
       </c>
       <c r="D24" t="n">
-        <v>8.58</v>
+        <v>16.47</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1061,79 +1061,79 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SKU20</t>
+          <t>SKU18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'model__alpha': 0.0003585298072319365, 'model__l1_ratio': 1.0}</t>
+          <t>{'model__n_neighbors': 3, 'model__weights': 'distance', 'model__p': 1, 'model__leaf_size': 36, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>55.34</v>
+        <v>56.57</v>
       </c>
       <c r="D25" t="n">
-        <v>14.06</v>
+        <v>56.57</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SKU19</t>
+          <t>SKU15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'model__alpha': 125.32145724611838, 'model__l1_ratio': 1.0}</t>
+          <t>{'max_depth': 4, 'learning_rate': 0.065, 'n_estimators': 50, 'subsample': 0.86, 'colsample_bytree': 0.88, 'gamma': 19.0, 'reg_alpha': 17.5, 'reg_lambda': 12.0, 'min_child_weight': 15}</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>65.65000000000001</v>
+        <v>68.73</v>
       </c>
       <c r="D26" t="n">
-        <v>27.08</v>
+        <v>16.41</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>XGBRegressor</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SKU8</t>
+          <t>SKU19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'model__alpha': 233.75241321673985, 'model__l1_ratio': 1.0}</t>
+          <t>{'model__n_neighbors': 4, 'model__weights': 'uniform', 'model__p': 1, 'model__leaf_size': 42, 'model__algorithm': 'ball_tree'}</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>72.02</v>
+        <v>69.95</v>
       </c>
       <c r="D27" t="n">
-        <v>12.98</v>
+        <v>25.68</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
+          <t>KNeighborsRegressor</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
